--- a/storage/templates/Bar_Salon.xlsx
+++ b/storage/templates/Bar_Salon.xlsx
@@ -305,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -406,6 +406,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -736,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN198"/>
+  <dimension ref="A1:AN220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="1" min="1" max="1"/>
@@ -14007,59 +14010,1577 @@
         <v/>
       </c>
     </row>
-    <row r="197" ht="22.05" customHeight="1">
-      <c r="C197" s="8">
-        <f>SUM(C7:C196)</f>
-        <v/>
-      </c>
-      <c r="E197" s="11" t="inlineStr">
+    <row r="197" ht="25.05" customHeight="1">
+      <c r="A197" s="35" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="B197" s="35" t="inlineStr">
+        <is>
+          <t>GIN BOMBAY ORIGINAL 70 CL</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>11.36275</v>
+      </c>
+      <c r="F197" s="13">
+        <f>C197*E197</f>
+        <v/>
+      </c>
+      <c r="G197" s="20" t="n"/>
+      <c r="H197" s="20" t="n"/>
+      <c r="I197" s="20" t="n"/>
+      <c r="J197" s="20" t="n"/>
+      <c r="K197" s="20" t="n"/>
+      <c r="L197" s="20" t="n"/>
+      <c r="M197" s="20" t="n"/>
+      <c r="N197" s="20" t="n"/>
+      <c r="O197" s="20" t="n"/>
+      <c r="P197" s="20" t="n"/>
+      <c r="Q197" s="20" t="n"/>
+      <c r="R197" s="20" t="n"/>
+      <c r="S197" s="20" t="n"/>
+      <c r="T197" s="20" t="n"/>
+      <c r="U197" s="20" t="n"/>
+      <c r="V197" s="20" t="n"/>
+      <c r="W197" s="20" t="n"/>
+      <c r="X197" s="20" t="n"/>
+      <c r="Y197" s="20" t="n"/>
+      <c r="Z197" s="20" t="n"/>
+      <c r="AA197" s="20" t="n"/>
+      <c r="AB197" s="20" t="n"/>
+      <c r="AC197" s="20" t="n"/>
+      <c r="AD197" s="20" t="n"/>
+      <c r="AE197" s="20" t="n"/>
+      <c r="AF197" s="20" t="n"/>
+      <c r="AG197" s="20" t="n"/>
+      <c r="AH197" s="20" t="n"/>
+      <c r="AI197" s="20" t="n"/>
+      <c r="AJ197" s="20" t="n"/>
+      <c r="AK197" s="20" t="n"/>
+      <c r="AL197" s="21">
+        <f>SUM(G197:AK197)</f>
+        <v/>
+      </c>
+      <c r="AM197" s="22">
+        <f>SUM(C197,AL197)</f>
+        <v/>
+      </c>
+      <c r="AN197" s="23">
+        <f>E197*AM197</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="25.05" customHeight="1">
+      <c r="A198" s="35" t="inlineStr">
+        <is>
+          <t>8982</t>
+        </is>
+      </c>
+      <c r="B198" s="35" t="inlineStr">
+        <is>
+          <t>CAVA CASTELL D'ORDAL RDO SEMI 75 CL</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E198" s="10" t="n">
+        <v>1.87147</v>
+      </c>
+      <c r="F198" s="13">
+        <f>C198*E198</f>
+        <v/>
+      </c>
+      <c r="G198" s="20" t="n"/>
+      <c r="H198" s="20" t="n"/>
+      <c r="I198" s="20" t="n"/>
+      <c r="J198" s="20" t="n"/>
+      <c r="K198" s="20" t="n"/>
+      <c r="L198" s="20" t="n"/>
+      <c r="M198" s="20" t="n"/>
+      <c r="N198" s="20" t="n"/>
+      <c r="O198" s="20" t="n"/>
+      <c r="P198" s="20" t="n"/>
+      <c r="Q198" s="20" t="n"/>
+      <c r="R198" s="20" t="n"/>
+      <c r="S198" s="20" t="n"/>
+      <c r="T198" s="20" t="n"/>
+      <c r="U198" s="20" t="n"/>
+      <c r="V198" s="20" t="n"/>
+      <c r="W198" s="20" t="n"/>
+      <c r="X198" s="20" t="n"/>
+      <c r="Y198" s="20" t="n"/>
+      <c r="Z198" s="20" t="n"/>
+      <c r="AA198" s="20" t="n"/>
+      <c r="AB198" s="20" t="n"/>
+      <c r="AC198" s="20" t="n"/>
+      <c r="AD198" s="20" t="n"/>
+      <c r="AE198" s="20" t="n"/>
+      <c r="AF198" s="20" t="n"/>
+      <c r="AG198" s="20" t="n"/>
+      <c r="AH198" s="20" t="n"/>
+      <c r="AI198" s="20" t="n"/>
+      <c r="AJ198" s="20" t="n"/>
+      <c r="AK198" s="20" t="n"/>
+      <c r="AL198" s="21">
+        <f>SUM(G198:AK198)</f>
+        <v/>
+      </c>
+      <c r="AM198" s="22">
+        <f>SUM(C198,AL198)</f>
+        <v/>
+      </c>
+      <c r="AN198" s="23">
+        <f>E198*AM198</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" ht="25.05" customHeight="1">
+      <c r="A199" s="35" t="inlineStr">
+        <is>
+          <t>8968</t>
+        </is>
+      </c>
+      <c r="B199" s="35" t="inlineStr">
+        <is>
+          <t>MEZCLA FRUTOS SECOS C/GALLETAS SALADAS 1.5 KG</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" s="36" t="inlineStr">
+        <is>
+          <t>BOTE</t>
+        </is>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F199" s="13">
+        <f>C199*E199</f>
+        <v/>
+      </c>
+      <c r="G199" s="20" t="n"/>
+      <c r="H199" s="20" t="n"/>
+      <c r="I199" s="20" t="n"/>
+      <c r="J199" s="20" t="n"/>
+      <c r="K199" s="20" t="n"/>
+      <c r="L199" s="20" t="n"/>
+      <c r="M199" s="20" t="n"/>
+      <c r="N199" s="20" t="n"/>
+      <c r="O199" s="20" t="n"/>
+      <c r="P199" s="20" t="n"/>
+      <c r="Q199" s="20" t="n"/>
+      <c r="R199" s="20" t="n"/>
+      <c r="S199" s="20" t="n"/>
+      <c r="T199" s="20" t="n"/>
+      <c r="U199" s="20" t="n"/>
+      <c r="V199" s="20" t="n"/>
+      <c r="W199" s="20" t="n"/>
+      <c r="X199" s="20" t="n"/>
+      <c r="Y199" s="20" t="n"/>
+      <c r="Z199" s="20" t="n"/>
+      <c r="AA199" s="20" t="n"/>
+      <c r="AB199" s="20" t="n"/>
+      <c r="AC199" s="20" t="n"/>
+      <c r="AD199" s="20" t="n"/>
+      <c r="AE199" s="20" t="n"/>
+      <c r="AF199" s="20" t="n"/>
+      <c r="AG199" s="20" t="n"/>
+      <c r="AH199" s="20" t="n"/>
+      <c r="AI199" s="20" t="n"/>
+      <c r="AJ199" s="20" t="n"/>
+      <c r="AK199" s="20" t="n"/>
+      <c r="AL199" s="21">
+        <f>SUM(G199:AK199)</f>
+        <v/>
+      </c>
+      <c r="AM199" s="22">
+        <f>SUM(C199,AL199)</f>
+        <v/>
+      </c>
+      <c r="AN199" s="23">
+        <f>E199*AM199</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" ht="25.05" customHeight="1">
+      <c r="A200" s="35" t="inlineStr">
+        <is>
+          <t>10360</t>
+        </is>
+      </c>
+      <c r="B200" s="35" t="inlineStr">
+        <is>
+          <t>TARRINA ARANDANOS 125-150 GR</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" s="36" t="inlineStr">
+        <is>
+          <t>TARRINA</t>
+        </is>
+      </c>
+      <c r="E200" s="10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F200" s="13">
+        <f>C200*E200</f>
+        <v/>
+      </c>
+      <c r="G200" s="20" t="n"/>
+      <c r="H200" s="20" t="n"/>
+      <c r="I200" s="20" t="n"/>
+      <c r="J200" s="20" t="n"/>
+      <c r="K200" s="20" t="n"/>
+      <c r="L200" s="20" t="n"/>
+      <c r="M200" s="20" t="n"/>
+      <c r="N200" s="20" t="n"/>
+      <c r="O200" s="20" t="n"/>
+      <c r="P200" s="20" t="n"/>
+      <c r="Q200" s="20" t="n"/>
+      <c r="R200" s="20" t="n"/>
+      <c r="S200" s="20" t="n"/>
+      <c r="T200" s="20" t="n"/>
+      <c r="U200" s="20" t="n"/>
+      <c r="V200" s="20" t="n"/>
+      <c r="W200" s="20" t="n"/>
+      <c r="X200" s="20" t="n"/>
+      <c r="Y200" s="20" t="n"/>
+      <c r="Z200" s="20" t="n"/>
+      <c r="AA200" s="20" t="n"/>
+      <c r="AB200" s="20" t="n"/>
+      <c r="AC200" s="20" t="n"/>
+      <c r="AD200" s="20" t="n"/>
+      <c r="AE200" s="20" t="n"/>
+      <c r="AF200" s="20" t="n"/>
+      <c r="AG200" s="20" t="n"/>
+      <c r="AH200" s="20" t="n"/>
+      <c r="AI200" s="20" t="n"/>
+      <c r="AJ200" s="20" t="n"/>
+      <c r="AK200" s="20" t="n"/>
+      <c r="AL200" s="21">
+        <f>SUM(G200:AK200)</f>
+        <v/>
+      </c>
+      <c r="AM200" s="22">
+        <f>SUM(C200,AL200)</f>
+        <v/>
+      </c>
+      <c r="AN200" s="23">
+        <f>E200*AM200</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" ht="25.05" customHeight="1">
+      <c r="A201" s="35" t="inlineStr">
+        <is>
+          <t>10361</t>
+        </is>
+      </c>
+      <c r="B201" s="35" t="inlineStr">
+        <is>
+          <t>MORA TARRINA 125-150 GR</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" s="36" t="inlineStr">
+        <is>
+          <t>TARRINA</t>
+        </is>
+      </c>
+      <c r="E201" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F201" s="13">
+        <f>C201*E201</f>
+        <v/>
+      </c>
+      <c r="G201" s="20" t="n"/>
+      <c r="H201" s="20" t="n"/>
+      <c r="I201" s="20" t="n"/>
+      <c r="J201" s="20" t="n"/>
+      <c r="K201" s="20" t="n"/>
+      <c r="L201" s="20" t="n"/>
+      <c r="M201" s="20" t="n"/>
+      <c r="N201" s="20" t="n"/>
+      <c r="O201" s="20" t="n"/>
+      <c r="P201" s="20" t="n"/>
+      <c r="Q201" s="20" t="n"/>
+      <c r="R201" s="20" t="n"/>
+      <c r="S201" s="20" t="n"/>
+      <c r="T201" s="20" t="n"/>
+      <c r="U201" s="20" t="n"/>
+      <c r="V201" s="20" t="n"/>
+      <c r="W201" s="20" t="n"/>
+      <c r="X201" s="20" t="n"/>
+      <c r="Y201" s="20" t="n"/>
+      <c r="Z201" s="20" t="n"/>
+      <c r="AA201" s="20" t="n"/>
+      <c r="AB201" s="20" t="n"/>
+      <c r="AC201" s="20" t="n"/>
+      <c r="AD201" s="20" t="n"/>
+      <c r="AE201" s="20" t="n"/>
+      <c r="AF201" s="20" t="n"/>
+      <c r="AG201" s="20" t="n"/>
+      <c r="AH201" s="20" t="n"/>
+      <c r="AI201" s="20" t="n"/>
+      <c r="AJ201" s="20" t="n"/>
+      <c r="AK201" s="20" t="n"/>
+      <c r="AL201" s="21">
+        <f>SUM(G201:AK201)</f>
+        <v/>
+      </c>
+      <c r="AM201" s="22">
+        <f>SUM(C201,AL201)</f>
+        <v/>
+      </c>
+      <c r="AN201" s="23">
+        <f>E201*AM201</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" ht="25.05" customHeight="1">
+      <c r="A202" s="35" t="inlineStr">
+        <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B202" s="35" t="inlineStr">
+        <is>
+          <t>TARRINA FRAMBUESAS 125-150 GR</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" s="36" t="inlineStr">
+        <is>
+          <t>TARRINA</t>
+        </is>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F202" s="13">
+        <f>C202*E202</f>
+        <v/>
+      </c>
+      <c r="G202" s="20" t="n"/>
+      <c r="H202" s="20" t="n"/>
+      <c r="I202" s="20" t="n"/>
+      <c r="J202" s="20" t="n"/>
+      <c r="K202" s="20" t="n"/>
+      <c r="L202" s="20" t="n"/>
+      <c r="M202" s="20" t="n"/>
+      <c r="N202" s="20" t="n"/>
+      <c r="O202" s="20" t="n"/>
+      <c r="P202" s="20" t="n"/>
+      <c r="Q202" s="20" t="n"/>
+      <c r="R202" s="20" t="n"/>
+      <c r="S202" s="20" t="n"/>
+      <c r="T202" s="20" t="n"/>
+      <c r="U202" s="20" t="n"/>
+      <c r="V202" s="20" t="n"/>
+      <c r="W202" s="20" t="n"/>
+      <c r="X202" s="20" t="n"/>
+      <c r="Y202" s="20" t="n"/>
+      <c r="Z202" s="20" t="n"/>
+      <c r="AA202" s="20" t="n"/>
+      <c r="AB202" s="20" t="n"/>
+      <c r="AC202" s="20" t="n"/>
+      <c r="AD202" s="20" t="n"/>
+      <c r="AE202" s="20" t="n"/>
+      <c r="AF202" s="20" t="n"/>
+      <c r="AG202" s="20" t="n"/>
+      <c r="AH202" s="20" t="n"/>
+      <c r="AI202" s="20" t="n"/>
+      <c r="AJ202" s="20" t="n"/>
+      <c r="AK202" s="20" t="n"/>
+      <c r="AL202" s="21">
+        <f>SUM(G202:AK202)</f>
+        <v/>
+      </c>
+      <c r="AM202" s="22">
+        <f>SUM(C202,AL202)</f>
+        <v/>
+      </c>
+      <c r="AN202" s="23">
+        <f>E202*AM202</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="25.05" customHeight="1">
+      <c r="A203" s="35" t="inlineStr">
+        <is>
+          <t>25133</t>
+        </is>
+      </c>
+      <c r="B203" s="35" t="inlineStr">
+        <is>
+          <t>CONOS QUESO/BACON 650 GR</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" s="36" t="inlineStr">
+        <is>
+          <t>PAQUETE</t>
+        </is>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="F203" s="13">
+        <f>C203*E203</f>
+        <v/>
+      </c>
+      <c r="G203" s="20" t="n"/>
+      <c r="H203" s="20" t="n"/>
+      <c r="I203" s="20" t="n"/>
+      <c r="J203" s="20" t="n"/>
+      <c r="K203" s="20" t="n"/>
+      <c r="L203" s="20" t="n"/>
+      <c r="M203" s="20" t="n"/>
+      <c r="N203" s="20" t="n"/>
+      <c r="O203" s="20" t="n"/>
+      <c r="P203" s="20" t="n"/>
+      <c r="Q203" s="20" t="n"/>
+      <c r="R203" s="20" t="n"/>
+      <c r="S203" s="20" t="n"/>
+      <c r="T203" s="20" t="n"/>
+      <c r="U203" s="20" t="n"/>
+      <c r="V203" s="20" t="n"/>
+      <c r="W203" s="20" t="n"/>
+      <c r="X203" s="20" t="n"/>
+      <c r="Y203" s="20" t="n"/>
+      <c r="Z203" s="20" t="n"/>
+      <c r="AA203" s="20" t="n"/>
+      <c r="AB203" s="20" t="n"/>
+      <c r="AC203" s="20" t="n"/>
+      <c r="AD203" s="20" t="n"/>
+      <c r="AE203" s="20" t="n"/>
+      <c r="AF203" s="20" t="n"/>
+      <c r="AG203" s="20" t="n"/>
+      <c r="AH203" s="20" t="n"/>
+      <c r="AI203" s="20" t="n"/>
+      <c r="AJ203" s="20" t="n"/>
+      <c r="AK203" s="20" t="n"/>
+      <c r="AL203" s="21">
+        <f>SUM(G203:AK203)</f>
+        <v/>
+      </c>
+      <c r="AM203" s="22">
+        <f>SUM(C203,AL203)</f>
+        <v/>
+      </c>
+      <c r="AN203" s="23">
+        <f>E203*AM203</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" ht="25.05" customHeight="1">
+      <c r="A204" s="35" t="inlineStr">
+        <is>
+          <t>25134</t>
+        </is>
+      </c>
+      <c r="B204" s="35" t="inlineStr">
+        <is>
+          <t>SNACK KASKYS 1 KG</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" s="36" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="E204" s="10" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="F204" s="13">
+        <f>C204*E204</f>
+        <v/>
+      </c>
+      <c r="G204" s="20" t="n"/>
+      <c r="H204" s="20" t="n"/>
+      <c r="I204" s="20" t="n"/>
+      <c r="J204" s="20" t="n"/>
+      <c r="K204" s="20" t="n"/>
+      <c r="L204" s="20" t="n"/>
+      <c r="M204" s="20" t="n"/>
+      <c r="N204" s="20" t="n"/>
+      <c r="O204" s="20" t="n"/>
+      <c r="P204" s="20" t="n"/>
+      <c r="Q204" s="20" t="n"/>
+      <c r="R204" s="20" t="n"/>
+      <c r="S204" s="20" t="n"/>
+      <c r="T204" s="20" t="n"/>
+      <c r="U204" s="20" t="n"/>
+      <c r="V204" s="20" t="n"/>
+      <c r="W204" s="20" t="n"/>
+      <c r="X204" s="20" t="n"/>
+      <c r="Y204" s="20" t="n"/>
+      <c r="Z204" s="20" t="n"/>
+      <c r="AA204" s="20" t="n"/>
+      <c r="AB204" s="20" t="n"/>
+      <c r="AC204" s="20" t="n"/>
+      <c r="AD204" s="20" t="n"/>
+      <c r="AE204" s="20" t="n"/>
+      <c r="AF204" s="20" t="n"/>
+      <c r="AG204" s="20" t="n"/>
+      <c r="AH204" s="20" t="n"/>
+      <c r="AI204" s="20" t="n"/>
+      <c r="AJ204" s="20" t="n"/>
+      <c r="AK204" s="20" t="n"/>
+      <c r="AL204" s="21">
+        <f>SUM(G204:AK204)</f>
+        <v/>
+      </c>
+      <c r="AM204" s="22">
+        <f>SUM(C204,AL204)</f>
+        <v/>
+      </c>
+      <c r="AN204" s="23">
+        <f>E204*AM204</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" ht="25.05" customHeight="1">
+      <c r="A205" s="35" t="inlineStr">
+        <is>
+          <t>5868</t>
+        </is>
+      </c>
+      <c r="B205" s="35" t="inlineStr">
+        <is>
+          <t>PISTACHO REPELADO CRUDO</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" s="36" t="inlineStr">
+        <is>
+          <t>KILO</t>
+        </is>
+      </c>
+      <c r="E205" s="10" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="F205" s="13">
+        <f>C205*E205</f>
+        <v/>
+      </c>
+      <c r="G205" s="20" t="n"/>
+      <c r="H205" s="20" t="n"/>
+      <c r="I205" s="20" t="n"/>
+      <c r="J205" s="20" t="n"/>
+      <c r="K205" s="20" t="n"/>
+      <c r="L205" s="20" t="n"/>
+      <c r="M205" s="20" t="n"/>
+      <c r="N205" s="20" t="n"/>
+      <c r="O205" s="20" t="n"/>
+      <c r="P205" s="20" t="n"/>
+      <c r="Q205" s="20" t="n"/>
+      <c r="R205" s="20" t="n"/>
+      <c r="S205" s="20" t="n"/>
+      <c r="T205" s="20" t="n"/>
+      <c r="U205" s="20" t="n"/>
+      <c r="V205" s="20" t="n"/>
+      <c r="W205" s="20" t="n"/>
+      <c r="X205" s="20" t="n"/>
+      <c r="Y205" s="20" t="n"/>
+      <c r="Z205" s="20" t="n"/>
+      <c r="AA205" s="20" t="n"/>
+      <c r="AB205" s="20" t="n"/>
+      <c r="AC205" s="20" t="n"/>
+      <c r="AD205" s="20" t="n"/>
+      <c r="AE205" s="20" t="n"/>
+      <c r="AF205" s="20" t="n"/>
+      <c r="AG205" s="20" t="n"/>
+      <c r="AH205" s="20" t="n"/>
+      <c r="AI205" s="20" t="n"/>
+      <c r="AJ205" s="20" t="n"/>
+      <c r="AK205" s="20" t="n"/>
+      <c r="AL205" s="21">
+        <f>SUM(G205:AK205)</f>
+        <v/>
+      </c>
+      <c r="AM205" s="22">
+        <f>SUM(C205,AL205)</f>
+        <v/>
+      </c>
+      <c r="AN205" s="23">
+        <f>E205*AM205</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="25.05" customHeight="1">
+      <c r="A206" s="35" t="inlineStr">
+        <is>
+          <t>24707</t>
+        </is>
+      </c>
+      <c r="B206" s="35" t="inlineStr">
+        <is>
+          <t>VINO BCO BARBADILLO MOSCATO FRIZZANTE 75 CL</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E206" s="10" t="n">
+        <v>4.73759</v>
+      </c>
+      <c r="F206" s="13">
+        <f>C206*E206</f>
+        <v/>
+      </c>
+      <c r="G206" s="20" t="n"/>
+      <c r="H206" s="20" t="n"/>
+      <c r="I206" s="20" t="n"/>
+      <c r="J206" s="20" t="n"/>
+      <c r="K206" s="20" t="n"/>
+      <c r="L206" s="20" t="n"/>
+      <c r="M206" s="20" t="n"/>
+      <c r="N206" s="20" t="n"/>
+      <c r="O206" s="20" t="n"/>
+      <c r="P206" s="20" t="n"/>
+      <c r="Q206" s="20" t="n"/>
+      <c r="R206" s="20" t="n"/>
+      <c r="S206" s="20" t="n"/>
+      <c r="T206" s="20" t="n"/>
+      <c r="U206" s="20" t="n"/>
+      <c r="V206" s="20" t="n"/>
+      <c r="W206" s="20" t="n"/>
+      <c r="X206" s="20" t="n"/>
+      <c r="Y206" s="20" t="n"/>
+      <c r="Z206" s="20" t="n"/>
+      <c r="AA206" s="20" t="n"/>
+      <c r="AB206" s="20" t="n"/>
+      <c r="AC206" s="20" t="n"/>
+      <c r="AD206" s="20" t="n"/>
+      <c r="AE206" s="20" t="n"/>
+      <c r="AF206" s="20" t="n"/>
+      <c r="AG206" s="20" t="n"/>
+      <c r="AH206" s="20" t="n"/>
+      <c r="AI206" s="20" t="n"/>
+      <c r="AJ206" s="20" t="n"/>
+      <c r="AK206" s="20" t="n"/>
+      <c r="AL206" s="21">
+        <f>SUM(G206:AK206)</f>
+        <v/>
+      </c>
+      <c r="AM206" s="22">
+        <f>SUM(C206,AL206)</f>
+        <v/>
+      </c>
+      <c r="AN206" s="23">
+        <f>E206*AM206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" ht="25.05" customHeight="1">
+      <c r="A207" s="35" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="B207" s="35" t="inlineStr">
+        <is>
+          <t>NARANJA Nº 4</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" s="36" t="inlineStr">
+        <is>
+          <t>KILO</t>
+        </is>
+      </c>
+      <c r="E207" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F207" s="13">
+        <f>C207*E207</f>
+        <v/>
+      </c>
+      <c r="G207" s="20" t="n"/>
+      <c r="H207" s="20" t="n"/>
+      <c r="I207" s="20" t="n"/>
+      <c r="J207" s="20" t="n"/>
+      <c r="K207" s="20" t="n"/>
+      <c r="L207" s="20" t="n"/>
+      <c r="M207" s="20" t="n"/>
+      <c r="N207" s="20" t="n"/>
+      <c r="O207" s="20" t="n"/>
+      <c r="P207" s="20" t="n"/>
+      <c r="Q207" s="20" t="n"/>
+      <c r="R207" s="20" t="n"/>
+      <c r="S207" s="20" t="n"/>
+      <c r="T207" s="20" t="n"/>
+      <c r="U207" s="20" t="n"/>
+      <c r="V207" s="20" t="n"/>
+      <c r="W207" s="20" t="n"/>
+      <c r="X207" s="20" t="n"/>
+      <c r="Y207" s="20" t="n"/>
+      <c r="Z207" s="20" t="n"/>
+      <c r="AA207" s="20" t="n"/>
+      <c r="AB207" s="20" t="n"/>
+      <c r="AC207" s="20" t="n"/>
+      <c r="AD207" s="20" t="n"/>
+      <c r="AE207" s="20" t="n"/>
+      <c r="AF207" s="20" t="n"/>
+      <c r="AG207" s="20" t="n"/>
+      <c r="AH207" s="20" t="n"/>
+      <c r="AI207" s="20" t="n"/>
+      <c r="AJ207" s="20" t="n"/>
+      <c r="AK207" s="20" t="n"/>
+      <c r="AL207" s="21">
+        <f>SUM(G207:AK207)</f>
+        <v/>
+      </c>
+      <c r="AM207" s="22">
+        <f>SUM(C207,AL207)</f>
+        <v/>
+      </c>
+      <c r="AN207" s="23">
+        <f>E207*AM207</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="25.05" customHeight="1">
+      <c r="A208" s="35" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="B208" s="35" t="inlineStr">
+        <is>
+          <t>CAFE CONGELADO</t>
+        </is>
+      </c>
+      <c r="C208" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" s="36" t="inlineStr">
+        <is>
+          <t>BRIK</t>
+        </is>
+      </c>
+      <c r="E208" s="10" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="F208" s="13">
+        <f>C208*E208</f>
+        <v/>
+      </c>
+      <c r="G208" s="20" t="n"/>
+      <c r="H208" s="20" t="n"/>
+      <c r="I208" s="20" t="n"/>
+      <c r="J208" s="20" t="n"/>
+      <c r="K208" s="20" t="n"/>
+      <c r="L208" s="20" t="n"/>
+      <c r="M208" s="20" t="n"/>
+      <c r="N208" s="20" t="n"/>
+      <c r="O208" s="20" t="n"/>
+      <c r="P208" s="20" t="n"/>
+      <c r="Q208" s="20" t="n"/>
+      <c r="R208" s="20" t="n"/>
+      <c r="S208" s="20" t="n"/>
+      <c r="T208" s="20" t="n"/>
+      <c r="U208" s="20" t="n"/>
+      <c r="V208" s="20" t="n"/>
+      <c r="W208" s="20" t="n"/>
+      <c r="X208" s="20" t="n"/>
+      <c r="Y208" s="20" t="n"/>
+      <c r="Z208" s="20" t="n"/>
+      <c r="AA208" s="20" t="n"/>
+      <c r="AB208" s="20" t="n"/>
+      <c r="AC208" s="20" t="n"/>
+      <c r="AD208" s="20" t="n"/>
+      <c r="AE208" s="20" t="n"/>
+      <c r="AF208" s="20" t="n"/>
+      <c r="AG208" s="20" t="n"/>
+      <c r="AH208" s="20" t="n"/>
+      <c r="AI208" s="20" t="n"/>
+      <c r="AJ208" s="20" t="n"/>
+      <c r="AK208" s="20" t="n"/>
+      <c r="AL208" s="21">
+        <f>SUM(G208:AK208)</f>
+        <v/>
+      </c>
+      <c r="AM208" s="22">
+        <f>SUM(C208,AL208)</f>
+        <v/>
+      </c>
+      <c r="AN208" s="23">
+        <f>E208*AM208</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="25.05" customHeight="1">
+      <c r="A209" s="35" t="inlineStr">
+        <is>
+          <t>5343</t>
+        </is>
+      </c>
+      <c r="B209" s="35" t="inlineStr">
+        <is>
+          <t>LECHE CONCENTRADA MAQUINA 2 LT</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" s="36" t="inlineStr">
+        <is>
+          <t>BRIK</t>
+        </is>
+      </c>
+      <c r="E209" s="10" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="F209" s="13">
+        <f>C209*E209</f>
+        <v/>
+      </c>
+      <c r="G209" s="20" t="n"/>
+      <c r="H209" s="20" t="n"/>
+      <c r="I209" s="20" t="n"/>
+      <c r="J209" s="20" t="n"/>
+      <c r="K209" s="20" t="n"/>
+      <c r="L209" s="20" t="n"/>
+      <c r="M209" s="20" t="n"/>
+      <c r="N209" s="20" t="n"/>
+      <c r="O209" s="20" t="n"/>
+      <c r="P209" s="20" t="n"/>
+      <c r="Q209" s="20" t="n"/>
+      <c r="R209" s="20" t="n"/>
+      <c r="S209" s="20" t="n"/>
+      <c r="T209" s="20" t="n"/>
+      <c r="U209" s="20" t="n"/>
+      <c r="V209" s="20" t="n"/>
+      <c r="W209" s="20" t="n"/>
+      <c r="X209" s="20" t="n"/>
+      <c r="Y209" s="20" t="n"/>
+      <c r="Z209" s="20" t="n"/>
+      <c r="AA209" s="20" t="n"/>
+      <c r="AB209" s="20" t="n"/>
+      <c r="AC209" s="20" t="n"/>
+      <c r="AD209" s="20" t="n"/>
+      <c r="AE209" s="20" t="n"/>
+      <c r="AF209" s="20" t="n"/>
+      <c r="AG209" s="20" t="n"/>
+      <c r="AH209" s="20" t="n"/>
+      <c r="AI209" s="20" t="n"/>
+      <c r="AJ209" s="20" t="n"/>
+      <c r="AK209" s="20" t="n"/>
+      <c r="AL209" s="21">
+        <f>SUM(G209:AK209)</f>
+        <v/>
+      </c>
+      <c r="AM209" s="22">
+        <f>SUM(C209,AL209)</f>
+        <v/>
+      </c>
+      <c r="AN209" s="23">
+        <f>E209*AM209</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="25.05" customHeight="1">
+      <c r="A210" s="35" t="inlineStr">
+        <is>
+          <t>10363</t>
+        </is>
+      </c>
+      <c r="B210" s="35" t="inlineStr">
+        <is>
+          <t>GROSELLAS TARRINA 150 GR</t>
+        </is>
+      </c>
+      <c r="C210" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" s="36" t="inlineStr">
+        <is>
+          <t>TARRINA</t>
+        </is>
+      </c>
+      <c r="E210" s="10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F210" s="13">
+        <f>C210*E210</f>
+        <v/>
+      </c>
+      <c r="G210" s="20" t="n"/>
+      <c r="H210" s="20" t="n"/>
+      <c r="I210" s="20" t="n"/>
+      <c r="J210" s="20" t="n"/>
+      <c r="K210" s="20" t="n"/>
+      <c r="L210" s="20" t="n"/>
+      <c r="M210" s="20" t="n"/>
+      <c r="N210" s="20" t="n"/>
+      <c r="O210" s="20" t="n"/>
+      <c r="P210" s="20" t="n"/>
+      <c r="Q210" s="20" t="n"/>
+      <c r="R210" s="20" t="n"/>
+      <c r="S210" s="20" t="n"/>
+      <c r="T210" s="20" t="n"/>
+      <c r="U210" s="20" t="n"/>
+      <c r="V210" s="20" t="n"/>
+      <c r="W210" s="20" t="n"/>
+      <c r="X210" s="20" t="n"/>
+      <c r="Y210" s="20" t="n"/>
+      <c r="Z210" s="20" t="n"/>
+      <c r="AA210" s="20" t="n"/>
+      <c r="AB210" s="20" t="n"/>
+      <c r="AC210" s="20" t="n"/>
+      <c r="AD210" s="20" t="n"/>
+      <c r="AE210" s="20" t="n"/>
+      <c r="AF210" s="20" t="n"/>
+      <c r="AG210" s="20" t="n"/>
+      <c r="AH210" s="20" t="n"/>
+      <c r="AI210" s="20" t="n"/>
+      <c r="AJ210" s="20" t="n"/>
+      <c r="AK210" s="20" t="n"/>
+      <c r="AL210" s="21">
+        <f>SUM(G210:AK210)</f>
+        <v/>
+      </c>
+      <c r="AM210" s="22">
+        <f>SUM(C210,AL210)</f>
+        <v/>
+      </c>
+      <c r="AN210" s="23">
+        <f>E210*AM210</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" ht="25.05" customHeight="1">
+      <c r="A211" s="35" t="inlineStr">
+        <is>
+          <t>15093</t>
+        </is>
+      </c>
+      <c r="B211" s="35" t="inlineStr">
+        <is>
+          <t>ZUMO NARANJA 5 L</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" s="36" t="inlineStr">
+        <is>
+          <t>LITRO</t>
+        </is>
+      </c>
+      <c r="E211" s="10" t="n">
+        <v>2.60415</v>
+      </c>
+      <c r="F211" s="13">
+        <f>C211*E211</f>
+        <v/>
+      </c>
+      <c r="G211" s="20" t="n"/>
+      <c r="H211" s="20" t="n"/>
+      <c r="I211" s="20" t="n"/>
+      <c r="J211" s="20" t="n"/>
+      <c r="K211" s="20" t="n"/>
+      <c r="L211" s="20" t="n"/>
+      <c r="M211" s="20" t="n"/>
+      <c r="N211" s="20" t="n"/>
+      <c r="O211" s="20" t="n"/>
+      <c r="P211" s="20" t="n"/>
+      <c r="Q211" s="20" t="n"/>
+      <c r="R211" s="20" t="n"/>
+      <c r="S211" s="20" t="n"/>
+      <c r="T211" s="20" t="n"/>
+      <c r="U211" s="20" t="n"/>
+      <c r="V211" s="20" t="n"/>
+      <c r="W211" s="20" t="n"/>
+      <c r="X211" s="20" t="n"/>
+      <c r="Y211" s="20" t="n"/>
+      <c r="Z211" s="20" t="n"/>
+      <c r="AA211" s="20" t="n"/>
+      <c r="AB211" s="20" t="n"/>
+      <c r="AC211" s="20" t="n"/>
+      <c r="AD211" s="20" t="n"/>
+      <c r="AE211" s="20" t="n"/>
+      <c r="AF211" s="20" t="n"/>
+      <c r="AG211" s="20" t="n"/>
+      <c r="AH211" s="20" t="n"/>
+      <c r="AI211" s="20" t="n"/>
+      <c r="AJ211" s="20" t="n"/>
+      <c r="AK211" s="20" t="n"/>
+      <c r="AL211" s="21">
+        <f>SUM(G211:AK211)</f>
+        <v/>
+      </c>
+      <c r="AM211" s="22">
+        <f>SUM(C211,AL211)</f>
+        <v/>
+      </c>
+      <c r="AN211" s="23">
+        <f>E211*AM211</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" ht="25.05" customHeight="1">
+      <c r="A212" s="35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B212" s="35" t="inlineStr">
+        <is>
+          <t>WHISKY J &amp; B 70 CL</t>
+        </is>
+      </c>
+      <c r="C212" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E212" s="10" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="F212" s="13">
+        <f>C212*E212</f>
+        <v/>
+      </c>
+      <c r="G212" s="20" t="n"/>
+      <c r="H212" s="20" t="n"/>
+      <c r="I212" s="20" t="n"/>
+      <c r="J212" s="20" t="n"/>
+      <c r="K212" s="20" t="n"/>
+      <c r="L212" s="20" t="n"/>
+      <c r="M212" s="20" t="n"/>
+      <c r="N212" s="20" t="n"/>
+      <c r="O212" s="20" t="n"/>
+      <c r="P212" s="20" t="n"/>
+      <c r="Q212" s="20" t="n"/>
+      <c r="R212" s="20" t="n"/>
+      <c r="S212" s="20" t="n"/>
+      <c r="T212" s="20" t="n"/>
+      <c r="U212" s="20" t="n"/>
+      <c r="V212" s="20" t="n"/>
+      <c r="W212" s="20" t="n"/>
+      <c r="X212" s="20" t="n"/>
+      <c r="Y212" s="20" t="n"/>
+      <c r="Z212" s="20" t="n"/>
+      <c r="AA212" s="20" t="n"/>
+      <c r="AB212" s="20" t="n"/>
+      <c r="AC212" s="20" t="n"/>
+      <c r="AD212" s="20" t="n"/>
+      <c r="AE212" s="20" t="n"/>
+      <c r="AF212" s="20" t="n"/>
+      <c r="AG212" s="20" t="n"/>
+      <c r="AH212" s="20" t="n"/>
+      <c r="AI212" s="20" t="n"/>
+      <c r="AJ212" s="20" t="n"/>
+      <c r="AK212" s="20" t="n"/>
+      <c r="AL212" s="21">
+        <f>SUM(G212:AK212)</f>
+        <v/>
+      </c>
+      <c r="AM212" s="22">
+        <f>SUM(C212,AL212)</f>
+        <v/>
+      </c>
+      <c r="AN212" s="23">
+        <f>E212*AM212</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" ht="25.05" customHeight="1">
+      <c r="A213" s="35" t="inlineStr">
+        <is>
+          <t>5043</t>
+        </is>
+      </c>
+      <c r="B213" s="35" t="inlineStr">
+        <is>
+          <t>VODKA SMIRNOFF ROJA 70 CL</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E213" s="10" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="F213" s="13">
+        <f>C213*E213</f>
+        <v/>
+      </c>
+      <c r="G213" s="20" t="n"/>
+      <c r="H213" s="20" t="n"/>
+      <c r="I213" s="20" t="n"/>
+      <c r="J213" s="20" t="n"/>
+      <c r="K213" s="20" t="n"/>
+      <c r="L213" s="20" t="n"/>
+      <c r="M213" s="20" t="n"/>
+      <c r="N213" s="20" t="n"/>
+      <c r="O213" s="20" t="n"/>
+      <c r="P213" s="20" t="n"/>
+      <c r="Q213" s="20" t="n"/>
+      <c r="R213" s="20" t="n"/>
+      <c r="S213" s="20" t="n"/>
+      <c r="T213" s="20" t="n"/>
+      <c r="U213" s="20" t="n"/>
+      <c r="V213" s="20" t="n"/>
+      <c r="W213" s="20" t="n"/>
+      <c r="X213" s="20" t="n"/>
+      <c r="Y213" s="20" t="n"/>
+      <c r="Z213" s="20" t="n"/>
+      <c r="AA213" s="20" t="n"/>
+      <c r="AB213" s="20" t="n"/>
+      <c r="AC213" s="20" t="n"/>
+      <c r="AD213" s="20" t="n"/>
+      <c r="AE213" s="20" t="n"/>
+      <c r="AF213" s="20" t="n"/>
+      <c r="AG213" s="20" t="n"/>
+      <c r="AH213" s="20" t="n"/>
+      <c r="AI213" s="20" t="n"/>
+      <c r="AJ213" s="20" t="n"/>
+      <c r="AK213" s="20" t="n"/>
+      <c r="AL213" s="21">
+        <f>SUM(G213:AK213)</f>
+        <v/>
+      </c>
+      <c r="AM213" s="22">
+        <f>SUM(C213,AL213)</f>
+        <v/>
+      </c>
+      <c r="AN213" s="23">
+        <f>E213*AM213</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" ht="25.05" customHeight="1">
+      <c r="A214" s="35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B214" s="35" t="inlineStr">
+        <is>
+          <t>VODKA SMIRNOFF ROJA 100 CL</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E214" s="10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F214" s="13">
+        <f>C214*E214</f>
+        <v/>
+      </c>
+      <c r="G214" s="20" t="n"/>
+      <c r="H214" s="20" t="n"/>
+      <c r="I214" s="20" t="n"/>
+      <c r="J214" s="20" t="n"/>
+      <c r="K214" s="20" t="n"/>
+      <c r="L214" s="20" t="n"/>
+      <c r="M214" s="20" t="n"/>
+      <c r="N214" s="20" t="n"/>
+      <c r="O214" s="20" t="n"/>
+      <c r="P214" s="20" t="n"/>
+      <c r="Q214" s="20" t="n"/>
+      <c r="R214" s="20" t="n"/>
+      <c r="S214" s="20" t="n"/>
+      <c r="T214" s="20" t="n"/>
+      <c r="U214" s="20" t="n"/>
+      <c r="V214" s="20" t="n"/>
+      <c r="W214" s="20" t="n"/>
+      <c r="X214" s="20" t="n"/>
+      <c r="Y214" s="20" t="n"/>
+      <c r="Z214" s="20" t="n"/>
+      <c r="AA214" s="20" t="n"/>
+      <c r="AB214" s="20" t="n"/>
+      <c r="AC214" s="20" t="n"/>
+      <c r="AD214" s="20" t="n"/>
+      <c r="AE214" s="20" t="n"/>
+      <c r="AF214" s="20" t="n"/>
+      <c r="AG214" s="20" t="n"/>
+      <c r="AH214" s="20" t="n"/>
+      <c r="AI214" s="20" t="n"/>
+      <c r="AJ214" s="20" t="n"/>
+      <c r="AK214" s="20" t="n"/>
+      <c r="AL214" s="21">
+        <f>SUM(G214:AK214)</f>
+        <v/>
+      </c>
+      <c r="AM214" s="22">
+        <f>SUM(C214,AL214)</f>
+        <v/>
+      </c>
+      <c r="AN214" s="23">
+        <f>E214*AM214</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" ht="25.05" customHeight="1">
+      <c r="A215" s="35" t="inlineStr">
+        <is>
+          <t>11231</t>
+        </is>
+      </c>
+      <c r="B215" s="35" t="inlineStr">
+        <is>
+          <t>CHIPS VEGETALES 500-600 GR</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" s="36" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="E215" s="10" t="n">
+        <v>6.171</v>
+      </c>
+      <c r="F215" s="13">
+        <f>C215*E215</f>
+        <v/>
+      </c>
+      <c r="G215" s="20" t="n"/>
+      <c r="H215" s="20" t="n"/>
+      <c r="I215" s="20" t="n"/>
+      <c r="J215" s="20" t="n"/>
+      <c r="K215" s="20" t="n"/>
+      <c r="L215" s="20" t="n"/>
+      <c r="M215" s="20" t="n"/>
+      <c r="N215" s="20" t="n"/>
+      <c r="O215" s="20" t="n"/>
+      <c r="P215" s="20" t="n"/>
+      <c r="Q215" s="20" t="n"/>
+      <c r="R215" s="20" t="n"/>
+      <c r="S215" s="20" t="n"/>
+      <c r="T215" s="20" t="n"/>
+      <c r="U215" s="20" t="n"/>
+      <c r="V215" s="20" t="n"/>
+      <c r="W215" s="20" t="n"/>
+      <c r="X215" s="20" t="n"/>
+      <c r="Y215" s="20" t="n"/>
+      <c r="Z215" s="20" t="n"/>
+      <c r="AA215" s="20" t="n"/>
+      <c r="AB215" s="20" t="n"/>
+      <c r="AC215" s="20" t="n"/>
+      <c r="AD215" s="20" t="n"/>
+      <c r="AE215" s="20" t="n"/>
+      <c r="AF215" s="20" t="n"/>
+      <c r="AG215" s="20" t="n"/>
+      <c r="AH215" s="20" t="n"/>
+      <c r="AI215" s="20" t="n"/>
+      <c r="AJ215" s="20" t="n"/>
+      <c r="AK215" s="20" t="n"/>
+      <c r="AL215" s="21">
+        <f>SUM(G215:AK215)</f>
+        <v/>
+      </c>
+      <c r="AM215" s="22">
+        <f>SUM(C215,AL215)</f>
+        <v/>
+      </c>
+      <c r="AN215" s="23">
+        <f>E215*AM215</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" ht="25.05" customHeight="1">
+      <c r="A216" s="35" t="inlineStr">
+        <is>
+          <t>10121</t>
+        </is>
+      </c>
+      <c r="B216" s="35" t="inlineStr">
+        <is>
+          <t>CAVA PINKY S/ALCOHOL 75 CL (NIÑOS)</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E216" s="10" t="n">
+        <v>4.32778</v>
+      </c>
+      <c r="F216" s="13">
+        <f>C216*E216</f>
+        <v/>
+      </c>
+      <c r="G216" s="20" t="n"/>
+      <c r="H216" s="20" t="n"/>
+      <c r="I216" s="20" t="n"/>
+      <c r="J216" s="20" t="n"/>
+      <c r="K216" s="20" t="n"/>
+      <c r="L216" s="20" t="n"/>
+      <c r="M216" s="20" t="n"/>
+      <c r="N216" s="20" t="n"/>
+      <c r="O216" s="20" t="n"/>
+      <c r="P216" s="20" t="n"/>
+      <c r="Q216" s="20" t="n"/>
+      <c r="R216" s="20" t="n"/>
+      <c r="S216" s="20" t="n"/>
+      <c r="T216" s="20" t="n"/>
+      <c r="U216" s="20" t="n"/>
+      <c r="V216" s="20" t="n"/>
+      <c r="W216" s="20" t="n"/>
+      <c r="X216" s="20" t="n"/>
+      <c r="Y216" s="20" t="n"/>
+      <c r="Z216" s="20" t="n"/>
+      <c r="AA216" s="20" t="n"/>
+      <c r="AB216" s="20" t="n"/>
+      <c r="AC216" s="20" t="n"/>
+      <c r="AD216" s="20" t="n"/>
+      <c r="AE216" s="20" t="n"/>
+      <c r="AF216" s="20" t="n"/>
+      <c r="AG216" s="20" t="n"/>
+      <c r="AH216" s="20" t="n"/>
+      <c r="AI216" s="20" t="n"/>
+      <c r="AJ216" s="20" t="n"/>
+      <c r="AK216" s="20" t="n"/>
+      <c r="AL216" s="21">
+        <f>SUM(G216:AK216)</f>
+        <v/>
+      </c>
+      <c r="AM216" s="22">
+        <f>SUM(C216,AL216)</f>
+        <v/>
+      </c>
+      <c r="AN216" s="23">
+        <f>E216*AM216</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" ht="25.05" customHeight="1">
+      <c r="A217" s="35" t="inlineStr">
+        <is>
+          <t>26949</t>
+        </is>
+      </c>
+      <c r="B217" s="35" t="inlineStr">
+        <is>
+          <t>CERVEZA ALHAMBRA RESERVA 1925 C/R 33 CL</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" s="36" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E217" s="10" t="n">
+        <v>0.76072</v>
+      </c>
+      <c r="F217" s="13">
+        <f>C217*E217</f>
+        <v/>
+      </c>
+      <c r="G217" s="20" t="n"/>
+      <c r="H217" s="20" t="n"/>
+      <c r="I217" s="20" t="n"/>
+      <c r="J217" s="20" t="n"/>
+      <c r="K217" s="20" t="n"/>
+      <c r="L217" s="20" t="n"/>
+      <c r="M217" s="20" t="n"/>
+      <c r="N217" s="20" t="n"/>
+      <c r="O217" s="20" t="n"/>
+      <c r="P217" s="20" t="n"/>
+      <c r="Q217" s="20" t="n"/>
+      <c r="R217" s="20" t="n"/>
+      <c r="S217" s="20" t="n"/>
+      <c r="T217" s="20" t="n"/>
+      <c r="U217" s="20" t="n"/>
+      <c r="V217" s="20" t="n"/>
+      <c r="W217" s="20" t="n"/>
+      <c r="X217" s="20" t="n"/>
+      <c r="Y217" s="20" t="n"/>
+      <c r="Z217" s="20" t="n"/>
+      <c r="AA217" s="20" t="n"/>
+      <c r="AB217" s="20" t="n"/>
+      <c r="AC217" s="20" t="n"/>
+      <c r="AD217" s="20" t="n"/>
+      <c r="AE217" s="20" t="n"/>
+      <c r="AF217" s="20" t="n"/>
+      <c r="AG217" s="20" t="n"/>
+      <c r="AH217" s="20" t="n"/>
+      <c r="AI217" s="20" t="n"/>
+      <c r="AJ217" s="20" t="n"/>
+      <c r="AK217" s="20" t="n"/>
+      <c r="AL217" s="21">
+        <f>SUM(G217:AK217)</f>
+        <v/>
+      </c>
+      <c r="AM217" s="22">
+        <f>SUM(C217,AL217)</f>
+        <v/>
+      </c>
+      <c r="AN217" s="23">
+        <f>E217*AM217</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="25.05" customHeight="1">
+      <c r="A218" s="35" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="B218" s="35" t="inlineStr">
+        <is>
+          <t>SIROPE FRESA</t>
+        </is>
+      </c>
+      <c r="C218" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" s="36" t="inlineStr">
+        <is>
+          <t>BOTE</t>
+        </is>
+      </c>
+      <c r="E218" s="10" t="n">
+        <v>3.52133</v>
+      </c>
+      <c r="F218" s="13">
+        <f>C218*E218</f>
+        <v/>
+      </c>
+      <c r="G218" s="20" t="n"/>
+      <c r="H218" s="20" t="n"/>
+      <c r="I218" s="20" t="n"/>
+      <c r="J218" s="20" t="n"/>
+      <c r="K218" s="20" t="n"/>
+      <c r="L218" s="20" t="n"/>
+      <c r="M218" s="20" t="n"/>
+      <c r="N218" s="20" t="n"/>
+      <c r="O218" s="20" t="n"/>
+      <c r="P218" s="20" t="n"/>
+      <c r="Q218" s="20" t="n"/>
+      <c r="R218" s="20" t="n"/>
+      <c r="S218" s="20" t="n"/>
+      <c r="T218" s="20" t="n"/>
+      <c r="U218" s="20" t="n"/>
+      <c r="V218" s="20" t="n"/>
+      <c r="W218" s="20" t="n"/>
+      <c r="X218" s="20" t="n"/>
+      <c r="Y218" s="20" t="n"/>
+      <c r="Z218" s="20" t="n"/>
+      <c r="AA218" s="20" t="n"/>
+      <c r="AB218" s="20" t="n"/>
+      <c r="AC218" s="20" t="n"/>
+      <c r="AD218" s="20" t="n"/>
+      <c r="AE218" s="20" t="n"/>
+      <c r="AF218" s="20" t="n"/>
+      <c r="AG218" s="20" t="n"/>
+      <c r="AH218" s="20" t="n"/>
+      <c r="AI218" s="20" t="n"/>
+      <c r="AJ218" s="20" t="n"/>
+      <c r="AK218" s="20" t="n"/>
+      <c r="AL218" s="21">
+        <f>SUM(G218:AK218)</f>
+        <v/>
+      </c>
+      <c r="AM218" s="22">
+        <f>SUM(C218,AL218)</f>
+        <v/>
+      </c>
+      <c r="AN218" s="23">
+        <f>E218*AM218</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" ht="22.05" customHeight="1">
+      <c r="C219" s="8">
+        <f>SUM(C7:C218)</f>
+        <v/>
+      </c>
+      <c r="E219" s="11" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F197" s="12">
-        <f>SUM(F7:F196)</f>
-        <v/>
-      </c>
-      <c r="AL197" s="8">
-        <f>SUM(AL7:AL196)</f>
-        <v/>
-      </c>
-      <c r="AM197" s="8">
-        <f>SUM(AM7:AM196)</f>
-        <v/>
-      </c>
-      <c r="AN197" s="24">
-        <f>SUM(AN7:AN196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="22.05" customHeight="1">
-      <c r="E198" s="4" t="n"/>
-      <c r="F198" s="4" t="n"/>
-    </row>
-    <row r="199" ht="22.05" customHeight="1"/>
-    <row r="200" ht="22.05" customHeight="1"/>
-    <row r="201" ht="22.05" customHeight="1"/>
-    <row r="202" ht="22.05" customHeight="1"/>
-    <row r="203" ht="22.05" customHeight="1"/>
-    <row r="204" ht="22.05" customHeight="1"/>
-    <row r="205" ht="22.05" customHeight="1"/>
-    <row r="206" ht="22.05" customHeight="1"/>
-    <row r="207" ht="22.05" customHeight="1"/>
-    <row r="208" ht="22.05" customHeight="1"/>
-    <row r="209" ht="22.05" customHeight="1"/>
-    <row r="210" ht="22.05" customHeight="1"/>
-    <row r="211" ht="22.05" customHeight="1"/>
-    <row r="212" ht="22.05" customHeight="1"/>
-    <row r="213" ht="22.05" customHeight="1"/>
-    <row r="214" ht="22.05" customHeight="1"/>
-    <row r="215" ht="22.05" customHeight="1"/>
-    <row r="216" ht="22.05" customHeight="1"/>
-    <row r="217" ht="22.05" customHeight="1"/>
-    <row r="218" ht="22.05" customHeight="1"/>
-    <row r="219" ht="22.05" customHeight="1"/>
-    <row r="220" ht="22.05" customHeight="1"/>
+      <c r="F219" s="12">
+        <f>SUM(F7:F218)</f>
+        <v/>
+      </c>
+      <c r="AL219" s="8">
+        <f>SUM(AL7:AL218)</f>
+        <v/>
+      </c>
+      <c r="AM219" s="8">
+        <f>SUM(AM7:AM218)</f>
+        <v/>
+      </c>
+      <c r="AN219" s="24">
+        <f>SUM(AN7:AN218)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" ht="22.05" customHeight="1">
+      <c r="E220" s="4" t="n"/>
+      <c r="F220" s="4" t="n"/>
+    </row>
     <row r="221" ht="22.05" customHeight="1"/>
     <row r="222" ht="22.05" customHeight="1"/>
     <row r="223" ht="22.05" customHeight="1"/>
